--- a/SacredElement.xlsx
+++ b/SacredElement.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Jitesh\Desktop\hem-catalogue-app_final-1\hem-catalogue-app-1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\product catalogue\product catalogue app v2\.claude\worktrees\youthful-dhawan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08FF1A79-DA0B-4CF5-914D-3766A2DADD05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC2CC1C-2AE2-4ECD-99AB-D8F20399B969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{DBC07F3F-378B-484D-90AD-F709C710C6B9}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$86</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="172">
   <si>
     <t>Category</t>
   </si>
@@ -74,15 +74,9 @@
     <t>Smudge Organic Bomb - White Sage</t>
   </si>
   <si>
-    <t>CLAY INCENSE BURNER</t>
-  </si>
-  <si>
     <t>WITCHCRAFT POUCH</t>
   </si>
   <si>
-    <t>Terra Clay Incense Burner</t>
-  </si>
-  <si>
     <t>QATARI POWDER HEXA PACK</t>
   </si>
   <si>
@@ -284,9 +278,6 @@
     <t>SH White Sage Organic Ball</t>
   </si>
   <si>
-    <t>SH Clay Incense Burner</t>
-  </si>
-  <si>
     <t>SH Witch Whisper Scent Pouch</t>
   </si>
   <si>
@@ -489,9 +480,6 @@
   </si>
   <si>
     <t xml:space="preserve">Citrus Herbal </t>
-  </si>
-  <si>
-    <t>Clay Incense Burner</t>
   </si>
   <si>
     <t>Enchanted Smoke</t>
@@ -1070,7 +1058,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60D7FE7C-11EF-4516-9D9A-706DE80968F0}">
-  <dimension ref="A1:H88"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr defaultColWidth="12.453125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45.453125" style="2" bestFit="1" customWidth="1"/>
@@ -1109,7 +1097,7 @@
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -1120,7 +1108,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -1131,7 +1119,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -1142,906 +1130,884 @@
         <v>10</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>13</v>
+      <c r="C6" s="7" t="s">
+        <v>147</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>150</v>
+      <c r="C7" s="7" t="s">
+        <v>148</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>153</v>
+        <v>11</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>151</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>154</v>
+        <v>11</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>152</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>155</v>
+      <c r="C12" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>156</v>
+      <c r="C13" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>18</v>
+        <v>166</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>19</v>
+        <v>169</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>170</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>174</v>
+        <v>18</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>168</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>175</v>
+        <v>18</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>167</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>172</v>
+        <v>19</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>157</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>171</v>
+        <v>19</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>158</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>165</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>21</v>
+      <c r="A30" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>166</v>
+        <v>22</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D34" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C35" s="2" t="s">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="C36" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>41</v>
+        <v>163</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>167</v>
+        <v>42</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>44</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>49</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>57</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>58</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>59</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>63</v>
+        <v>153</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>64</v>
+        <v>154</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>159</v>
+        <v>63</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>65</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>66</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>76</v>
+        <v>141</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>68</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>76</v>
+        <v>141</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>70</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>72</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C81" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D81" s="2" t="s">
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
+      <c r="C83" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C83" s="2" t="s">
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C84" s="2" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A88" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E88" xr:uid="{60D7FE7C-11EF-4516-9D9A-706DE80968F0}"/>
+  <autoFilter ref="A1:E86" xr:uid="{60D7FE7C-11EF-4516-9D9A-706DE80968F0}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/SacredElement.xlsx
+++ b/SacredElement.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\product catalogue\product catalogue app v2\.claude\worktrees\youthful-dhawan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC2CC1C-2AE2-4ECD-99AB-D8F20399B969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F782FAD-7E7A-4477-9BE0-C20BCBD6940C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{DBC07F3F-378B-484D-90AD-F709C710C6B9}"/>
   </bookViews>

--- a/SacredElement.xlsx
+++ b/SacredElement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F782FAD-7E7A-4477-9BE0-C20BCBD6940C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0B4874E-7A6E-4CC0-9900-6E213D361979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{DBC07F3F-378B-484D-90AD-F709C710C6B9}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="174">
   <si>
     <t>Category</t>
   </si>
@@ -200,9 +200,6 @@
     <t>ENERGY CLEANSING KIT</t>
   </si>
   <si>
-    <t xml:space="preserve">Sacred Element Organic Incense Sticks 10 sticks </t>
-  </si>
-  <si>
     <t>Red Rose Orgainc Incense Sticks</t>
   </si>
   <si>
@@ -221,9 +218,6 @@
     <t>White Sage Orgainc Incense Sticks</t>
   </si>
   <si>
-    <t xml:space="preserve">Sacred Element Organic Incense Sticks 8 sticks </t>
-  </si>
-  <si>
     <t xml:space="preserve">SH Musk Sacred Element-OS </t>
   </si>
   <si>
@@ -555,6 +549,18 @@
   </si>
   <si>
     <t>New Beginnings incense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sacred Element Organic Incense Sticks 10 </t>
+  </si>
+  <si>
+    <t>Sacred Element Organic Incense Sticks 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sacred Element Organic Incense Sticks 8 </t>
+  </si>
+  <si>
+    <t>Sacred Element Organic Incense Sticks 8</t>
   </si>
 </sst>
 </file>
@@ -1097,7 +1103,7 @@
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -1108,7 +1114,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -1119,7 +1125,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -1130,7 +1136,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -1138,10 +1144,10 @@
         <v>11</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -1149,10 +1155,10 @@
         <v>11</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -1160,10 +1166,10 @@
         <v>11</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -1171,10 +1177,10 @@
         <v>11</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -1182,10 +1188,10 @@
         <v>11</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -1193,10 +1199,10 @@
         <v>11</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
@@ -1207,7 +1213,7 @@
         <v>13</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
@@ -1218,7 +1224,7 @@
         <v>14</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
@@ -1229,7 +1235,7 @@
         <v>15</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -1240,7 +1246,7 @@
         <v>16</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -1251,7 +1257,7 @@
         <v>17</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -1259,10 +1265,10 @@
         <v>18</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -1270,10 +1276,10 @@
         <v>18</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -1281,10 +1287,10 @@
         <v>18</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -1292,10 +1298,10 @@
         <v>18</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -1303,10 +1309,10 @@
         <v>18</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -1314,10 +1320,10 @@
         <v>18</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -1325,10 +1331,10 @@
         <v>19</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -1336,10 +1342,10 @@
         <v>19</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -1347,10 +1353,10 @@
         <v>19</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -1358,10 +1364,10 @@
         <v>19</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -1369,10 +1375,10 @@
         <v>19</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -1380,10 +1386,10 @@
         <v>19</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -1394,7 +1400,7 @@
         <v>21</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -1405,7 +1411,7 @@
         <v>22</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -1416,7 +1422,7 @@
         <v>23</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -1427,7 +1433,7 @@
         <v>24</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -1438,7 +1444,7 @@
         <v>25</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -1449,7 +1455,7 @@
         <v>26</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -1460,7 +1466,7 @@
         <v>28</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -1471,7 +1477,7 @@
         <v>29</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -1482,7 +1488,7 @@
         <v>30</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -1493,7 +1499,7 @@
         <v>32</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -1504,7 +1510,7 @@
         <v>33</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -1515,7 +1521,7 @@
         <v>34</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -1526,7 +1532,7 @@
         <v>35</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
@@ -1537,7 +1543,7 @@
         <v>36</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -1548,7 +1554,7 @@
         <v>37</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
@@ -1559,7 +1565,7 @@
         <v>39</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -1570,7 +1576,7 @@
         <v>40</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
@@ -1578,10 +1584,10 @@
         <v>38</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -1592,7 +1598,7 @@
         <v>41</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
@@ -1603,7 +1609,7 @@
         <v>42</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
@@ -1614,7 +1620,7 @@
         <v>43</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
@@ -1625,7 +1631,7 @@
         <v>44</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
@@ -1636,7 +1642,7 @@
         <v>45</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
@@ -1647,7 +1653,7 @@
         <v>47</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
@@ -1658,7 +1664,7 @@
         <v>48</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
@@ -1669,7 +1675,7 @@
         <v>49</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
@@ -1680,7 +1686,7 @@
         <v>50</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
@@ -1691,7 +1697,7 @@
         <v>51</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
@@ -1702,308 +1708,308 @@
         <v>52</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="D58" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>53</v>
+        <v>170</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>53</v>
+        <v>171</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>53</v>
+        <v>171</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>53</v>
+        <v>171</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>53</v>
+        <v>171</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>60</v>
+        <v>172</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C65" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="D65" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>60</v>
+        <v>173</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>60</v>
+        <v>173</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>60</v>
+        <v>173</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>60</v>
+        <v>173</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/SacredElement.xlsx
+++ b/SacredElement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0B4874E-7A6E-4CC0-9900-6E213D361979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21979AA-3FA2-4CD5-8944-24D35977658B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{DBC07F3F-378B-484D-90AD-F709C710C6B9}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="173">
   <si>
     <t>Category</t>
   </si>
@@ -552,9 +552,6 @@
   </si>
   <si>
     <t xml:space="preserve">Sacred Element Organic Incense Sticks 10 </t>
-  </si>
-  <si>
-    <t>Sacred Element Organic Incense Sticks 10</t>
   </si>
   <si>
     <t xml:space="preserve">Sacred Element Organic Incense Sticks 8 </t>
@@ -1735,7 +1732,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>55</v>
@@ -1746,7 +1743,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>56</v>
@@ -1757,7 +1754,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>57</v>
@@ -1768,7 +1765,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>58</v>
@@ -1779,7 +1776,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>59</v>
@@ -1790,7 +1787,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>60</v>
@@ -1801,7 +1798,7 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>151</v>
@@ -1812,7 +1809,7 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>152</v>
@@ -1823,7 +1820,7 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>153</v>
@@ -1834,7 +1831,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>154</v>

--- a/SacredElement.xlsx
+++ b/SacredElement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21979AA-3FA2-4CD5-8944-24D35977658B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F96C17C0-7077-4550-98DF-6D11DB51A31A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{DBC07F3F-378B-484D-90AD-F709C710C6B9}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="172">
   <si>
     <t>Category</t>
   </si>
@@ -555,9 +555,6 @@
   </si>
   <si>
     <t xml:space="preserve">Sacred Element Organic Incense Sticks 8 </t>
-  </si>
-  <si>
-    <t>Sacred Element Organic Incense Sticks 8</t>
   </si>
 </sst>
 </file>
@@ -1787,7 +1784,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>60</v>
@@ -1798,7 +1795,7 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>151</v>
@@ -1809,7 +1806,7 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>152</v>
@@ -1820,7 +1817,7 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>153</v>
@@ -1831,7 +1828,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>154</v>

--- a/SacredElement.xlsx
+++ b/SacredElement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F96C17C0-7077-4550-98DF-6D11DB51A31A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7986F89D-C373-4175-AFD6-9AD859D800E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{DBC07F3F-378B-484D-90AD-F709C710C6B9}"/>
   </bookViews>
@@ -551,10 +551,10 @@
     <t>New Beginnings incense</t>
   </si>
   <si>
-    <t xml:space="preserve">Sacred Element Organic Incense Sticks 10 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sacred Element Organic Incense Sticks 8 </t>
+    <t>Sacred Element Organic Incense 10 Sticks</t>
+  </si>
+  <si>
+    <t>Sacred Element Organic Incense 8 Sticks</t>
   </si>
 </sst>
 </file>
